--- a/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
+++ b/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -266,22 +266,40 @@
     <t>item_medkit</t>
   </si>
   <si>
-    <t>绷带</t>
-  </si>
-  <si>
-    <t>恢复10点生命值</t>
-  </si>
-  <si>
-    <t>item_bandage</t>
-  </si>
-  <si>
-    <t>能量饮料</t>
-  </si>
-  <si>
-    <t>恢复40点能量</t>
-  </si>
-  <si>
-    <t>item_drink</t>
+    <t>霰弹枪1号</t>
+  </si>
+  <si>
+    <t>射程近，一次散射4发，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_shotgun</t>
+  </si>
+  <si>
+    <t>步枪1号</t>
+  </si>
+  <si>
+    <t>强制追踪，射速快，伤害高，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_rifle1</t>
+  </si>
+  <si>
+    <t>步枪2号</t>
+  </si>
+  <si>
+    <t>方向锁定，射程远，攻速快，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_rifle2</t>
+  </si>
+  <si>
+    <t>火箭炮1号</t>
+  </si>
+  <si>
+    <t>位置锁定，射程远，爆炸伤害，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_rocket</t>
   </si>
 </sst>
 </file>
@@ -769,164 +787,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1246,9 +1264,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.1666666666667" customWidth="1"/>
@@ -1266,7 +1284,7 @@
     <col min="13" max="13" width="19.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1319,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1336,7 +1354,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1357,7 +1375,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1392,7 +1410,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5">
       <c r="B5" s="1">
         <v>10001</v>
       </c>
@@ -1424,7 +1442,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6">
       <c r="B6" s="1">
         <v>10002</v>
       </c>
@@ -1456,7 +1474,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
@@ -1488,14 +1506,14 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8">
       <c r="B8" s="1">
         <v>10004</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="3">
@@ -1504,7 +1522,7 @@
       <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="0" t="s">
         <v>36</v>
       </c>
       <c r="H8" s="3">
@@ -1519,14 +1537,14 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9">
       <c r="B9" s="1">
         <v>10005</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="3">
@@ -1535,7 +1553,7 @@
       <c r="F9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="0" t="s">
         <v>39</v>
       </c>
       <c r="H9" s="3">
@@ -1548,14 +1566,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10">
       <c r="B10" s="1">
         <v>10006</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="0" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="3">
@@ -1564,7 +1582,7 @@
       <c r="F10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="0" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="3">
@@ -1577,14 +1595,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11">
       <c r="B11" s="1">
         <v>10007</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="3">
@@ -1593,7 +1611,7 @@
       <c r="F11" s="3">
         <v>1</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="0" t="s">
         <v>45</v>
       </c>
       <c r="H11" s="3">
@@ -1606,14 +1624,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12">
       <c r="B12" s="1">
         <v>10008</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="0" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="3">
@@ -1622,7 +1640,7 @@
       <c r="F12" s="3">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="0" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="3">
@@ -1635,14 +1653,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13">
       <c r="B13" s="1">
         <v>10009</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="3">
@@ -1651,7 +1669,7 @@
       <c r="F13" s="3">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="0" t="s">
         <v>51</v>
       </c>
       <c r="H13" s="3">
@@ -1664,14 +1682,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14">
       <c r="B14" s="1">
         <v>10010</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="0" t="s">
         <v>53</v>
       </c>
       <c r="E14" s="3">
@@ -1680,7 +1698,7 @@
       <c r="F14" s="3">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="0" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="3">
@@ -1693,14 +1711,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15">
       <c r="B15" s="1">
         <v>10011</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="0" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="3">
@@ -1709,7 +1727,7 @@
       <c r="F15" s="3">
         <v>1</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H15" s="3">
@@ -1722,14 +1740,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16">
       <c r="B16" s="1">
         <v>10012</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="0" t="s">
         <v>59</v>
       </c>
       <c r="E16" s="3">
@@ -1738,7 +1756,7 @@
       <c r="F16" s="3">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="0" t="s">
         <v>60</v>
       </c>
       <c r="H16" s="3">
@@ -1751,7 +1769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17">
       <c r="B17" s="5">
         <v>50001</v>
       </c>
@@ -1780,7 +1798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18">
       <c r="B18" s="5">
         <v>50002</v>
       </c>
@@ -1809,7 +1827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19">
       <c r="B19" s="5">
         <v>50003</v>
       </c>
@@ -1838,7 +1856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20">
       <c r="B20" s="5">
         <v>50004</v>
       </c>
@@ -1867,7 +1885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21">
       <c r="B21" s="5">
         <v>50005</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22">
       <c r="B22" s="5">
         <v>50006</v>
       </c>
@@ -1925,9 +1943,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23">
       <c r="B23" s="5">
-        <v>50007</v>
+        <v>50009</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>79</v>
@@ -1936,27 +1954,27 @@
         <v>80</v>
       </c>
       <c r="E23" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>81</v>
       </c>
       <c r="H23" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24">
       <c r="B24" s="5">
-        <v>50008</v>
+        <v>50010</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>82</v>
@@ -1965,21 +1983,79 @@
         <v>83</v>
       </c>
       <c r="E24" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="H24" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0">
+        <v>50011</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="0">
+        <v>1</v>
+      </c>
+      <c r="F25" s="0">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="0">
+        <v>3</v>
+      </c>
+      <c r="I25" s="0">
+        <v>0</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0">
+        <v>50012</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="0">
+        <v>1</v>
+      </c>
+      <c r="F26" s="0">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="0">
+        <v>4</v>
+      </c>
+      <c r="I26" s="0">
+        <v>0</v>
+      </c>
+      <c r="J26" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1988,4 +2064,9 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
+++ b/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05ET\MatchTest\ETGame\Packages\cn.etetet.item\Luban\Config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701E70B5-C104-4956-85CF-688C330669A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-30" yWindow="7770" windowWidth="28830" windowHeight="7830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
   <si>
     <t>##var</t>
   </si>
@@ -300,19 +306,25 @@
   </si>
   <si>
     <t>weapon_rocket</t>
+  </si>
+  <si>
+    <t>GridWidth</t>
+  </si>
+  <si>
+    <t>格子宽</t>
+  </si>
+  <si>
+    <t>GridHeight</t>
+  </si>
+  <si>
+    <t>格子高</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,151 +346,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,194 +365,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -686,323 +374,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1260,31 +662,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.1666666666667" customWidth="1"/>
-    <col min="2" max="2" width="10.8333333333333" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="20.1666666666667" customWidth="1"/>
-    <col min="5" max="5" width="5.66666666666667" customWidth="1"/>
-    <col min="6" max="6" width="9.16666666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
+    <col min="5" max="5" width="5.625" customWidth="1"/>
+    <col min="6" max="6" width="9.125" customWidth="1"/>
     <col min="7" max="7" width="35.5" customWidth="1"/>
     <col min="8" max="8" width="7.5" customWidth="1"/>
-    <col min="9" max="9" width="8.33333333333333" customWidth="1"/>
-    <col min="10" max="10" width="5.83333333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.375" customWidth="1"/>
+    <col min="10" max="10" width="5.875" customWidth="1"/>
     <col min="11" max="11" width="15.5" customWidth="1"/>
-    <col min="12" max="12" width="13.1666666666667" customWidth="1"/>
-    <col min="13" max="13" width="19.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="13" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1315,11 +717,15 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="K1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1350,11 +756,15 @@
       <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="M2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1371,11 +781,15 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="M3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1406,11 +820,15 @@
       <c r="J4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="M4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>10001</v>
       </c>
@@ -1438,11 +856,15 @@
       <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>10002</v>
       </c>
@@ -1470,11 +892,15 @@
       <c r="J6" s="1">
         <v>1</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
@@ -1502,18 +928,22 @@
       <c r="J7" s="1">
         <v>1</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>10004</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="3">
@@ -1522,7 +952,7 @@
       <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" t="s">
         <v>36</v>
       </c>
       <c r="H8" s="3">
@@ -1534,17 +964,21 @@
       <c r="J8" s="3">
         <v>1</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9">
+      <c r="K8" s="4">
+        <v>1</v>
+      </c>
+      <c r="L8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>10005</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="3">
@@ -1553,7 +987,7 @@
       <c r="F9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" t="s">
         <v>39</v>
       </c>
       <c r="H9" s="3">
@@ -1565,15 +999,21 @@
       <c r="J9" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>10006</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="3">
@@ -1582,7 +1022,7 @@
       <c r="F10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="3">
@@ -1594,15 +1034,21 @@
       <c r="J10" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>10007</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="3">
@@ -1611,7 +1057,7 @@
       <c r="F11" s="3">
         <v>1</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" t="s">
         <v>45</v>
       </c>
       <c r="H11" s="3">
@@ -1623,15 +1069,21 @@
       <c r="J11" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>10008</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="3">
@@ -1640,7 +1092,7 @@
       <c r="F12" s="3">
         <v>1</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="3">
@@ -1652,15 +1104,21 @@
       <c r="J12" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>10009</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="3">
@@ -1669,7 +1127,7 @@
       <c r="F13" s="3">
         <v>1</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" t="s">
         <v>51</v>
       </c>
       <c r="H13" s="3">
@@ -1681,15 +1139,21 @@
       <c r="J13" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
         <v>10010</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" t="s">
         <v>53</v>
       </c>
       <c r="E14" s="3">
@@ -1698,7 +1162,7 @@
       <c r="F14" s="3">
         <v>1</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="3">
@@ -1710,15 +1174,21 @@
       <c r="J14" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>10011</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="3">
@@ -1727,7 +1197,7 @@
       <c r="F15" s="3">
         <v>1</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" t="s">
         <v>57</v>
       </c>
       <c r="H15" s="3">
@@ -1739,15 +1209,21 @@
       <c r="J15" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <v>10012</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>59</v>
       </c>
       <c r="E16" s="3">
@@ -1756,7 +1232,7 @@
       <c r="F16" s="3">
         <v>1</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" t="s">
         <v>60</v>
       </c>
       <c r="H16" s="3">
@@ -1768,8 +1244,14 @@
       <c r="J16" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>50001</v>
       </c>
@@ -1797,8 +1279,14 @@
       <c r="J17" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="5">
         <v>50002</v>
       </c>
@@ -1826,8 +1314,14 @@
       <c r="J18" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="5">
         <v>50003</v>
       </c>
@@ -1855,8 +1349,14 @@
       <c r="J19" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="5">
         <v>50004</v>
       </c>
@@ -1884,8 +1384,14 @@
       <c r="J20" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="5">
         <v>50005</v>
       </c>
@@ -1913,8 +1419,14 @@
       <c r="J21" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="5">
         <v>50006</v>
       </c>
@@ -1942,8 +1454,14 @@
       <c r="J22" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="5">
         <v>50009</v>
       </c>
@@ -1971,8 +1489,14 @@
       <c r="J23" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="5">
         <v>50010</v>
       </c>
@@ -2000,73 +1524,86 @@
       <c r="J24" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="0">
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25">
         <v>50011</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="0">
-        <v>1</v>
-      </c>
-      <c r="F25" s="0">
-        <v>1</v>
-      </c>
-      <c r="G25" s="0" t="s">
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
         <v>87</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H25">
         <v>3</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="0">
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26">
         <v>50012</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="0">
-        <v>1</v>
-      </c>
-      <c r="F26" s="0">
-        <v>1</v>
-      </c>
-      <c r="G26" s="0" t="s">
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
         <v>90</v>
       </c>
-      <c r="H26" s="0">
+      <c r="H26">
         <v>4</v>
       </c>
-      <c r="I26" s="0">
+      <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="0">
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
+++ b/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.item/Luban/Config/Datas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDC1534-45C1-5340-9954-7F42F15AA305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11540" yWindow="4480" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
@@ -44,6 +38,33 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>MaxStack</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>UseType</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>GridWidth</t>
+  </si>
+  <si>
+    <t>GridHeight</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -53,28 +74,16 @@
     <t>string</t>
   </si>
   <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>MaxStack</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>UseType</t>
-  </si>
-  <si>
-    <t>Level</t>
+    <t>ID</t>
   </si>
   <si>
     <t>名称</t>
@@ -101,6 +110,12 @@
     <t>等级</t>
   </si>
   <si>
+    <t>格子宽</t>
+  </si>
+  <si>
+    <t>格子高</t>
+  </si>
+  <si>
     <t>生命药水</t>
   </si>
   <si>
@@ -128,10 +143,6 @@
     <t>Items/Ore_Iron</t>
   </si>
   <si>
-    <t>ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>新手之剑</t>
   </si>
   <si>
@@ -213,19 +224,71 @@
     <t>Items/Equipment/Ring_Strength_01</t>
   </si>
   <si>
-    <t>##group</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>霰弹枪1号</t>
+  </si>
+  <si>
+    <t>射程近，一次散射4发，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_shotgun</t>
+  </si>
+  <si>
+    <t>步枪1号</t>
+  </si>
+  <si>
+    <t>强制追踪，射速快，伤害高，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_rifle1</t>
+  </si>
+  <si>
+    <t>步枪2号</t>
+  </si>
+  <si>
+    <t>方向锁定，射程远，攻速快，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_rifle2</t>
+  </si>
+  <si>
+    <t>火箭炮1号</t>
+  </si>
+  <si>
+    <t>位置锁定，射程远，爆炸伤害，静止攻击</t>
+  </si>
+  <si>
+    <t>weapon_rocket</t>
+  </si>
+  <si>
+    <t>冲锋枪</t>
+  </si>
+  <si>
+    <t>weapon_smg</t>
+  </si>
+  <si>
+    <t>战术眼-示例</t>
+  </si>
+  <si>
+    <t>示例道具：向目标点投放一个临时视野单位</t>
+  </si>
+  <si>
+    <t>战术侦查-示例</t>
+  </si>
+  <si>
+    <t>示例道具：开启后揭示附近敌方眼位</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,29 +297,174 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="4"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,8 +477,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -278,34 +672,338 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -563,206 +1261,226 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="5.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="35.5" customWidth="1"/>
-    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" customWidth="1"/>
+    <col min="9" max="9" width="8.375" customWidth="1"/>
+    <col min="10" max="10" width="5.875" customWidth="1"/>
     <col min="11" max="11" width="15.5" customWidth="1"/>
-    <col min="12" max="12" width="13.1640625" customWidth="1"/>
-    <col min="13" max="13" width="19.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="13" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="5"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5" s="6">
+        <v>10001</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="6">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="B5" s="3">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="6">
+        <v>10002</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="6">
         <v>2</v>
       </c>
-      <c r="F5" s="3">
-        <v>99</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6" s="3">
-        <v>10002</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>99</v>
+      <c r="F6" s="6">
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H6" s="3">
         <v>1</v>
@@ -773,28 +1491,32 @@
       <c r="J6" s="3">
         <v>1</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>10003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3">
+        <v>36</v>
+      </c>
+      <c r="E7" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="3">
-        <v>999</v>
+      <c r="F7" s="6">
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -805,276 +1527,577 @@
       <c r="J7" s="3">
         <v>1</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="B8" s="3">
+      <c r="B8" s="6">
         <v>10004</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="4">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2">
         <v>4</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>1</v>
       </c>
       <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" s="6">
+        <v>10005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>2</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="6">
+        <v>10006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7">
+        <v>2</v>
+      </c>
+      <c r="J10" s="7">
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" s="6">
+        <v>10007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>2</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12" s="6">
+        <v>10008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7">
+        <v>2</v>
+      </c>
+      <c r="J12" s="7">
+        <v>3</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13" s="6">
+        <v>10009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="2">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="7">
+        <v>1</v>
+      </c>
+      <c r="I13" s="7">
+        <v>2</v>
+      </c>
+      <c r="J13" s="7">
+        <v>5</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14" s="6">
+        <v>10010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="7">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7">
+        <v>2</v>
+      </c>
+      <c r="J14" s="7">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="B15" s="6">
+        <v>10011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="7">
+        <v>2</v>
+      </c>
+      <c r="I15" s="7">
+        <v>2</v>
+      </c>
+      <c r="J15" s="7">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="B16" s="6">
+        <v>10012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1</v>
+      </c>
+      <c r="I16" s="7">
+        <v>2</v>
+      </c>
+      <c r="J16" s="7">
+        <v>8</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="2">
+        <v>50009</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="8">
+        <v>3</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="2">
+        <v>50010</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="8">
+        <v>3</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="2">
+        <v>50011</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="2">
+        <v>50012</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="2:12">
+      <c r="B21" s="9">
+        <v>50013</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:12">
+      <c r="B22" s="11">
+        <v>60001</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="11">
+        <v>2</v>
+      </c>
+      <c r="F22" s="11">
+        <v>1</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="12">
+        <v>2</v>
+      </c>
+      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:12">
+      <c r="B23" s="11">
+        <v>60002</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="11">
+        <v>2</v>
+      </c>
+      <c r="F23" s="11">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="H23" s="1">
         <v>2</v>
       </c>
-      <c r="J8" s="4">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="B9" s="3">
-        <v>10005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="4">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4">
-        <v>2</v>
-      </c>
-      <c r="J9" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="3">
-        <v>10006</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="4">
-        <v>4</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4">
-        <v>2</v>
-      </c>
-      <c r="J10" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="B11" s="3">
-        <v>10007</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="4">
-        <v>4</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4">
-        <v>2</v>
-      </c>
-      <c r="J11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="B12" s="3">
-        <v>10008</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="4">
-        <v>4</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="3">
-        <v>10009</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="4">
-        <v>4</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4">
-        <v>2</v>
-      </c>
-      <c r="J13" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="B14" s="3">
-        <v>10010</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="4">
-        <v>4</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="4">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="B15" s="3">
-        <v>10011</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="4">
-        <v>4</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="4">
-        <v>2</v>
-      </c>
-      <c r="I15" s="4">
-        <v>2</v>
-      </c>
-      <c r="J15" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="B16" s="3">
-        <v>10012</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="4">
-        <v>4</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="4">
-        <v>1</v>
-      </c>
-      <c r="I16" s="4">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4">
-        <v>8</v>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
+++ b/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>##var</t>
   </si>
@@ -65,6 +65,36 @@
     <t>GridHeight</t>
   </si>
   <si>
+    <t>LoadoutShopVisible</t>
+  </si>
+  <si>
+    <t>LoadoutShopCategory</t>
+  </si>
+  <si>
+    <t>LoadoutBuyPrice</t>
+  </si>
+  <si>
+    <t>CanEquipMainWeapon</t>
+  </si>
+  <si>
+    <t>CanEquipSubWeapon</t>
+  </si>
+  <si>
+    <t>CanEquipArmor</t>
+  </si>
+  <si>
+    <t>CanEquipBackpack</t>
+  </si>
+  <si>
+    <t>IsBackpack</t>
+  </si>
+  <si>
+    <t>BackpackWidth</t>
+  </si>
+  <si>
+    <t>BackpackHeight</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -74,6 +104,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -116,6 +149,36 @@
     <t>格子高</t>
   </si>
   <si>
+    <t>起装商店可见</t>
+  </si>
+  <si>
+    <t>起装商店分类</t>
+  </si>
+  <si>
+    <t>起装购买价</t>
+  </si>
+  <si>
+    <t>可装备主武器槽</t>
+  </si>
+  <si>
+    <t>可装备副武器槽</t>
+  </si>
+  <si>
+    <t>可装备护甲槽</t>
+  </si>
+  <si>
+    <t>可装备背包槽</t>
+  </si>
+  <si>
+    <t>是否背包</t>
+  </si>
+  <si>
+    <t>背包宽</t>
+  </si>
+  <si>
+    <t>背包高</t>
+  </si>
+  <si>
     <t>生命药水</t>
   </si>
   <si>
@@ -276,6 +339,66 @@
   </si>
   <si>
     <t>示例道具：开启后揭示附近敌方眼位</t>
+  </si>
+  <si>
+    <t>轻型防弹衣 I</t>
+  </si>
+  <si>
+    <t>基础护甲，提供少量生命加成，适合新手起装</t>
+  </si>
+  <si>
+    <t>侦察护甲 II</t>
+  </si>
+  <si>
+    <t>兼顾生存与机动的中级护甲，适合常规跑局</t>
+  </si>
+  <si>
+    <t>突击护甲 III</t>
+  </si>
+  <si>
+    <t>更厚重的突击护甲，适合正面作战</t>
+  </si>
+  <si>
+    <t>重型护甲 IV</t>
+  </si>
+  <si>
+    <t>高等级重型护甲，大幅提升生存能力</t>
+  </si>
+  <si>
+    <t>侦察背包 I</t>
+  </si>
+  <si>
+    <t>基础 3x3 背包，适合轻装撤离</t>
+  </si>
+  <si>
+    <t>Items/Equipment/Backpack_Field_01</t>
+  </si>
+  <si>
+    <t>野战背包 II</t>
+  </si>
+  <si>
+    <t>标准 4x4 背包，兼顾容量与体积</t>
+  </si>
+  <si>
+    <t>Items/Equipment/Backpack_Field_02</t>
+  </si>
+  <si>
+    <t>突击背包 III</t>
+  </si>
+  <si>
+    <t>大容量 5x5 背包，适合中后期扫图</t>
+  </si>
+  <si>
+    <t>Items/Equipment/Backpack_Field_03</t>
+  </si>
+  <si>
+    <t>重装背包 IV</t>
+  </si>
+  <si>
+    <t>高容量 6x6 背包，适合高收益撤离</t>
+  </si>
+  <si>
+    <t>Items/Equipment/Backpack_Field_04</t>
   </si>
 </sst>
 </file>
@@ -773,165 +896,165 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -940,12 +1063,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1265,17 +1388,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1" style="2"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="5.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.625" customWidth="1" style="2"/>
+    <col min="6" max="6" width="9.125" customWidth="1" style="2"/>
     <col min="7" max="7" width="35.5" customWidth="1"/>
     <col min="8" max="8" width="7.5" customWidth="1"/>
     <col min="9" max="9" width="8.375" customWidth="1"/>
@@ -1285,7 +1408,7 @@
     <col min="13" max="13" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1322,120 +1445,201 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5"/>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" s="0" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="V4" s="0" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5">
       <c r="B5" s="6">
         <v>10001</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="E5" s="6">
         <v>2</v>
@@ -1444,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="H5" s="3">
         <v>1</v>
@@ -1461,17 +1665,46 @@
       <c r="L5" s="3">
         <v>1</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="0">
+        <v>4</v>
+      </c>
+      <c r="O5" s="0">
+        <v>80</v>
+      </c>
+      <c r="P5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="0">
+        <v>0</v>
+      </c>
+      <c r="V5" s="0">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6">
       <c r="B6" s="6">
         <v>10002</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -1480,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3">
         <v>1</v>
@@ -1497,17 +1730,46 @@
       <c r="L6" s="3">
         <v>1</v>
       </c>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" s="0">
+        <v>4</v>
+      </c>
+      <c r="O6" s="0">
+        <v>90</v>
+      </c>
+      <c r="P6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" s="0">
+        <v>0</v>
+      </c>
+      <c r="V6" s="0">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7">
       <c r="B7" s="6">
         <v>10003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E7" s="6">
         <v>3</v>
@@ -1516,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -1533,17 +1795,46 @@
       <c r="L7" s="3">
         <v>1</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0">
+        <v>5</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0</v>
+      </c>
+      <c r="P7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" s="0">
+        <v>0</v>
+      </c>
+      <c r="V7" s="0">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8">
       <c r="B8" s="6">
         <v>10004</v>
       </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
+      <c r="C8" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>60</v>
       </c>
       <c r="E8" s="2">
         <v>4</v>
@@ -1551,8 +1842,8 @@
       <c r="F8" s="2">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
-        <v>40</v>
+      <c r="G8" s="0" t="s">
+        <v>61</v>
       </c>
       <c r="H8" s="7">
         <v>0</v>
@@ -1569,16 +1860,46 @@
       <c r="L8" s="6">
         <v>1</v>
       </c>
+      <c r="M8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0">
+        <v>1</v>
+      </c>
+      <c r="O8" s="0">
+        <v>0</v>
+      </c>
+      <c r="P8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0</v>
+      </c>
+      <c r="V8" s="0">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9">
       <c r="B9" s="6">
         <v>10005</v>
       </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
+      <c r="C9" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="E9" s="2">
         <v>4</v>
@@ -1586,8 +1907,8 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
-        <v>43</v>
+      <c r="G9" s="0" t="s">
+        <v>64</v>
       </c>
       <c r="H9" s="7">
         <v>0</v>
@@ -1598,22 +1919,52 @@
       <c r="J9" s="7">
         <v>1</v>
       </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
+      <c r="K9" s="0">
+        <v>1</v>
+      </c>
+      <c r="L9" s="0">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0">
+        <v>2</v>
+      </c>
+      <c r="O9" s="0">
+        <v>0</v>
+      </c>
+      <c r="P9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" s="0">
+        <v>0</v>
+      </c>
+      <c r="V9" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10">
       <c r="B10" s="6">
         <v>10006</v>
       </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
+      <c r="C10" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="E10" s="2">
         <v>4</v>
@@ -1621,8 +1972,8 @@
       <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
-        <v>46</v>
+      <c r="G10" s="0" t="s">
+        <v>67</v>
       </c>
       <c r="H10" s="7">
         <v>1</v>
@@ -1633,22 +1984,52 @@
       <c r="J10" s="7">
         <v>5</v>
       </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
+      <c r="K10" s="0">
+        <v>1</v>
+      </c>
+      <c r="L10" s="0">
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0">
+        <v>2</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0</v>
+      </c>
+      <c r="P10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="0">
+        <v>0</v>
+      </c>
+      <c r="V10" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11">
       <c r="B11" s="6">
         <v>10007</v>
       </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
+      <c r="C11" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>69</v>
       </c>
       <c r="E11" s="2">
         <v>4</v>
@@ -1656,8 +2037,8 @@
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" t="s">
-        <v>49</v>
+      <c r="G11" s="0" t="s">
+        <v>70</v>
       </c>
       <c r="H11" s="7">
         <v>0</v>
@@ -1668,22 +2049,52 @@
       <c r="J11" s="7">
         <v>1</v>
       </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
+      <c r="K11" s="0">
+        <v>1</v>
+      </c>
+      <c r="L11" s="0">
+        <v>1</v>
+      </c>
+      <c r="M11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0">
+        <v>2</v>
+      </c>
+      <c r="O11" s="0">
+        <v>0</v>
+      </c>
+      <c r="P11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="0">
+        <v>0</v>
+      </c>
+      <c r="V11" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12">
       <c r="B12" s="6">
         <v>10008</v>
       </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
+      <c r="C12" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>72</v>
       </c>
       <c r="E12" s="2">
         <v>4</v>
@@ -1691,8 +2102,8 @@
       <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
-        <v>52</v>
+      <c r="G12" s="0" t="s">
+        <v>73</v>
       </c>
       <c r="H12" s="7">
         <v>0</v>
@@ -1703,22 +2114,52 @@
       <c r="J12" s="7">
         <v>3</v>
       </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
+      <c r="K12" s="0">
+        <v>1</v>
+      </c>
+      <c r="L12" s="0">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0">
+        <v>2</v>
+      </c>
+      <c r="O12" s="0">
+        <v>0</v>
+      </c>
+      <c r="P12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" s="0">
+        <v>0</v>
+      </c>
+      <c r="V12" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13">
       <c r="B13" s="6">
         <v>10009</v>
       </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
+      <c r="C13" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>75</v>
       </c>
       <c r="E13" s="2">
         <v>4</v>
@@ -1726,8 +2167,8 @@
       <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
-        <v>55</v>
+      <c r="G13" s="0" t="s">
+        <v>76</v>
       </c>
       <c r="H13" s="7">
         <v>1</v>
@@ -1738,22 +2179,52 @@
       <c r="J13" s="7">
         <v>5</v>
       </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
+      <c r="K13" s="0">
+        <v>1</v>
+      </c>
+      <c r="L13" s="0">
+        <v>1</v>
+      </c>
+      <c r="M13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0">
+        <v>2</v>
+      </c>
+      <c r="O13" s="0">
+        <v>0</v>
+      </c>
+      <c r="P13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" s="0">
+        <v>0</v>
+      </c>
+      <c r="V13" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14">
       <c r="B14" s="6">
         <v>10010</v>
       </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
+      <c r="C14" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>78</v>
       </c>
       <c r="E14" s="2">
         <v>4</v>
@@ -1761,8 +2232,8 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
-        <v>58</v>
+      <c r="G14" s="0" t="s">
+        <v>79</v>
       </c>
       <c r="H14" s="7">
         <v>1</v>
@@ -1773,22 +2244,52 @@
       <c r="J14" s="7">
         <v>5</v>
       </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
+      <c r="K14" s="0">
+        <v>1</v>
+      </c>
+      <c r="L14" s="0">
+        <v>1</v>
+      </c>
+      <c r="M14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0">
+        <v>1</v>
+      </c>
+      <c r="O14" s="0">
+        <v>0</v>
+      </c>
+      <c r="P14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="0">
+        <v>0</v>
+      </c>
+      <c r="V14" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15">
       <c r="B15" s="6">
         <v>10011</v>
       </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
+      <c r="C15" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>81</v>
       </c>
       <c r="E15" s="2">
         <v>4</v>
@@ -1796,8 +2297,8 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" t="s">
-        <v>61</v>
+      <c r="G15" s="0" t="s">
+        <v>82</v>
       </c>
       <c r="H15" s="7">
         <v>2</v>
@@ -1808,22 +2309,52 @@
       <c r="J15" s="7">
         <v>10</v>
       </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
+      <c r="K15" s="0">
+        <v>1</v>
+      </c>
+      <c r="L15" s="0">
+        <v>1</v>
+      </c>
+      <c r="M15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0">
+        <v>5</v>
+      </c>
+      <c r="O15" s="0">
+        <v>0</v>
+      </c>
+      <c r="P15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" s="0">
+        <v>0</v>
+      </c>
+      <c r="V15" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16">
       <c r="B16" s="6">
         <v>10012</v>
       </c>
-      <c r="C16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
+      <c r="C16" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>84</v>
       </c>
       <c r="E16" s="2">
         <v>4</v>
@@ -1831,8 +2362,8 @@
       <c r="F16" s="2">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
-        <v>64</v>
+      <c r="G16" s="0" t="s">
+        <v>85</v>
       </c>
       <c r="H16" s="7">
         <v>1</v>
@@ -1843,22 +2374,52 @@
       <c r="J16" s="7">
         <v>8</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
+      <c r="K16" s="0">
+        <v>1</v>
+      </c>
+      <c r="L16" s="0">
+        <v>1</v>
+      </c>
+      <c r="M16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0">
+        <v>5</v>
+      </c>
+      <c r="O16" s="0">
+        <v>0</v>
+      </c>
+      <c r="P16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" s="0">
+        <v>0</v>
+      </c>
+      <c r="V16" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17">
       <c r="B17" s="2">
         <v>50009</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1867,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="H17" s="8">
         <v>3</v>
@@ -1878,22 +2439,52 @@
       <c r="J17" s="8">
         <v>1</v>
       </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
+      <c r="K17" s="0">
+        <v>2</v>
+      </c>
+      <c r="L17" s="0">
+        <v>3</v>
+      </c>
+      <c r="M17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" s="0">
+        <v>1</v>
+      </c>
+      <c r="O17" s="0">
+        <v>1200</v>
+      </c>
+      <c r="P17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" s="0">
+        <v>0</v>
+      </c>
+      <c r="V17" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18">
       <c r="B18" s="2">
         <v>50010</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1902,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="H18" s="8">
         <v>3</v>
@@ -1913,22 +2504,52 @@
       <c r="J18" s="8">
         <v>1</v>
       </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
+      <c r="K18" s="0">
+        <v>2</v>
+      </c>
+      <c r="L18" s="0">
+        <v>4</v>
+      </c>
+      <c r="M18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" s="0">
+        <v>1</v>
+      </c>
+      <c r="O18" s="0">
+        <v>1400</v>
+      </c>
+      <c r="P18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" s="0">
+        <v>0</v>
+      </c>
+      <c r="V18" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19">
       <c r="B19" s="2">
         <v>50011</v>
       </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
+      <c r="C19" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>93</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -1936,34 +2557,64 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="G19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19">
+      <c r="G19" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="0">
         <v>3</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
+      <c r="I19" s="0">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0">
+        <v>1</v>
+      </c>
+      <c r="K19" s="0">
+        <v>2</v>
+      </c>
+      <c r="L19" s="0">
+        <v>4</v>
+      </c>
+      <c r="M19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" s="0">
+        <v>1</v>
+      </c>
+      <c r="O19" s="0">
+        <v>1600</v>
+      </c>
+      <c r="P19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" s="0">
+        <v>0</v>
+      </c>
+      <c r="V19" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20">
       <c r="B20" s="2">
         <v>50012</v>
       </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
+      <c r="C20" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>96</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -1971,34 +2622,64 @@
       <c r="F20" s="2">
         <v>1</v>
       </c>
-      <c r="G20" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="0">
         <v>4</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
+      <c r="I20" s="0">
+        <v>0</v>
+      </c>
+      <c r="J20" s="0">
+        <v>1</v>
+      </c>
+      <c r="K20" s="0">
+        <v>3</v>
+      </c>
+      <c r="L20" s="0">
+        <v>4</v>
+      </c>
+      <c r="M20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" s="0">
+        <v>1</v>
+      </c>
+      <c r="O20" s="0">
+        <v>2200</v>
+      </c>
+      <c r="P20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" s="0">
+        <v>0</v>
+      </c>
+      <c r="V20" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="2:12">
+    <row r="21">
       <c r="B21" s="9">
         <v>50013</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
+        <v>98</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>96</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -2006,34 +2687,64 @@
       <c r="F21" s="2">
         <v>1</v>
       </c>
-      <c r="G21" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21">
+      <c r="G21" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="0">
         <v>4</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
+      <c r="I21" s="0">
+        <v>0</v>
+      </c>
+      <c r="J21" s="0">
+        <v>1</v>
+      </c>
+      <c r="K21" s="0">
+        <v>2</v>
+      </c>
+      <c r="L21" s="0">
+        <v>3</v>
+      </c>
+      <c r="M21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" s="0">
+        <v>1</v>
+      </c>
+      <c r="O21" s="0">
+        <v>1800</v>
+      </c>
+      <c r="P21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" s="0">
+        <v>0</v>
+      </c>
+      <c r="V21" s="0">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:12">
+    <row r="22" s="1" customFormat="1">
       <c r="B22" s="11">
         <v>60001</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E22" s="11">
         <v>2</v>
@@ -2042,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="H22" s="12">
         <v>2</v>
@@ -2059,16 +2770,46 @@
       <c r="L22" s="1">
         <v>1</v>
       </c>
+      <c r="M22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>4</v>
+      </c>
+      <c r="O22" s="1">
+        <v>300</v>
+      </c>
+      <c r="P22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:12">
+    <row r="23" s="1" customFormat="1">
       <c r="B23" s="11">
         <v>60002</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="E23" s="11">
         <v>2</v>
@@ -2077,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H23" s="1">
         <v>2</v>
@@ -2093,6 +2834,556 @@
       </c>
       <c r="L23" s="1">
         <v>1</v>
+      </c>
+      <c r="M23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>4</v>
+      </c>
+      <c r="O23" s="1">
+        <v>350</v>
+      </c>
+      <c r="P23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="0">
+        <v>1</v>
+      </c>
+      <c r="I24" s="0">
+        <v>2</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1</v>
+      </c>
+      <c r="K24" s="0">
+        <v>2</v>
+      </c>
+      <c r="L24" s="0">
+        <v>2</v>
+      </c>
+      <c r="M24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" s="0">
+        <v>2</v>
+      </c>
+      <c r="O24" s="0">
+        <v>500</v>
+      </c>
+      <c r="P24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" s="0">
+        <v>0</v>
+      </c>
+      <c r="V24" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2">
+        <v>20002</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="0">
+        <v>2</v>
+      </c>
+      <c r="I25" s="0">
+        <v>2</v>
+      </c>
+      <c r="J25" s="0">
+        <v>4</v>
+      </c>
+      <c r="K25" s="0">
+        <v>2</v>
+      </c>
+      <c r="L25" s="0">
+        <v>2</v>
+      </c>
+      <c r="M25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" s="0">
+        <v>2</v>
+      </c>
+      <c r="O25" s="0">
+        <v>1100</v>
+      </c>
+      <c r="P25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" s="0">
+        <v>0</v>
+      </c>
+      <c r="V25" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2">
+        <v>20003</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="2">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H26" s="0">
+        <v>3</v>
+      </c>
+      <c r="I26" s="0">
+        <v>2</v>
+      </c>
+      <c r="J26" s="0">
+        <v>8</v>
+      </c>
+      <c r="K26" s="0">
+        <v>2</v>
+      </c>
+      <c r="L26" s="0">
+        <v>3</v>
+      </c>
+      <c r="M26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" s="0">
+        <v>2</v>
+      </c>
+      <c r="O26" s="0">
+        <v>2200</v>
+      </c>
+      <c r="P26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" s="0">
+        <v>0</v>
+      </c>
+      <c r="V26" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2">
+        <v>20004</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="0">
+        <v>4</v>
+      </c>
+      <c r="I27" s="0">
+        <v>2</v>
+      </c>
+      <c r="J27" s="0">
+        <v>12</v>
+      </c>
+      <c r="K27" s="0">
+        <v>3</v>
+      </c>
+      <c r="L27" s="0">
+        <v>3</v>
+      </c>
+      <c r="M27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" s="0">
+        <v>2</v>
+      </c>
+      <c r="O27" s="0">
+        <v>4200</v>
+      </c>
+      <c r="P27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" s="0">
+        <v>0</v>
+      </c>
+      <c r="V27" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2">
+        <v>21001</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="0">
+        <v>1</v>
+      </c>
+      <c r="I28" s="0">
+        <v>2</v>
+      </c>
+      <c r="J28" s="0">
+        <v>1</v>
+      </c>
+      <c r="K28" s="0">
+        <v>2</v>
+      </c>
+      <c r="L28" s="0">
+        <v>2</v>
+      </c>
+      <c r="M28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" s="0">
+        <v>3</v>
+      </c>
+      <c r="O28" s="0">
+        <v>600</v>
+      </c>
+      <c r="P28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" s="0">
+        <v>3</v>
+      </c>
+      <c r="V28" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2">
+        <v>21002</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="H29" s="0">
+        <v>2</v>
+      </c>
+      <c r="I29" s="0">
+        <v>2</v>
+      </c>
+      <c r="J29" s="0">
+        <v>4</v>
+      </c>
+      <c r="K29" s="0">
+        <v>2</v>
+      </c>
+      <c r="L29" s="0">
+        <v>3</v>
+      </c>
+      <c r="M29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" s="0">
+        <v>3</v>
+      </c>
+      <c r="O29" s="0">
+        <v>1400</v>
+      </c>
+      <c r="P29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" s="0">
+        <v>4</v>
+      </c>
+      <c r="V29" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2">
+        <v>21003</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="2">
+        <v>4</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="H30" s="0">
+        <v>3</v>
+      </c>
+      <c r="I30" s="0">
+        <v>2</v>
+      </c>
+      <c r="J30" s="0">
+        <v>8</v>
+      </c>
+      <c r="K30" s="0">
+        <v>3</v>
+      </c>
+      <c r="L30" s="0">
+        <v>3</v>
+      </c>
+      <c r="M30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" s="0">
+        <v>3</v>
+      </c>
+      <c r="O30" s="0">
+        <v>2800</v>
+      </c>
+      <c r="P30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" s="0">
+        <v>5</v>
+      </c>
+      <c r="V30" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2">
+        <v>21004</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="2">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="H31" s="0">
+        <v>4</v>
+      </c>
+      <c r="I31" s="0">
+        <v>2</v>
+      </c>
+      <c r="J31" s="0">
+        <v>12</v>
+      </c>
+      <c r="K31" s="0">
+        <v>3</v>
+      </c>
+      <c r="L31" s="0">
+        <v>4</v>
+      </c>
+      <c r="M31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" s="0">
+        <v>3</v>
+      </c>
+      <c r="O31" s="0">
+        <v>5200</v>
+      </c>
+      <c r="P31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" s="0">
+        <v>6</v>
+      </c>
+      <c r="V31" s="0">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2100,4 +3391,9 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
+++ b/Packages/cn.etetet.item/Luban/Config/Datas/Item.xlsx
@@ -185,7 +185,7 @@
     <t>射程近，一次散射4发，静止攻击</t>
   </si>
   <si>
-    <t>weapon_shotgun</t>
+    <t>export (40)_0</t>
   </si>
   <si>
     <t>步枪1号</t>
@@ -194,7 +194,7 @@
     <t>强制追踪，射速快，伤害高，静止攻击</t>
   </si>
   <si>
-    <t>weapon_rifle1</t>
+    <t>export (40)_1</t>
   </si>
   <si>
     <t>步枪2号</t>
@@ -203,7 +203,7 @@
     <t>方向锁定，射程远，攻速快，静止攻击</t>
   </si>
   <si>
-    <t>weapon_rifle2</t>
+    <t>export (40)_2</t>
   </si>
   <si>
     <t>火箭炮1号</t>
@@ -212,13 +212,13 @@
     <t>位置锁定，射程远，爆炸伤害，静止攻击</t>
   </si>
   <si>
-    <t>weapon_rocket</t>
+    <t>export (40)_3</t>
   </si>
   <si>
     <t>冲锋枪</t>
   </si>
   <si>
-    <t>weapon_smg</t>
+    <t>export (40)_4</t>
   </si>
   <si>
     <t>战术眼-示例</t>
@@ -1828,7 +1828,7 @@
       <c r="F7" s="2">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="6" t="s">
         <v>58</v>
       </c>
       <c r="H7">
@@ -1893,7 +1893,7 @@
       <c r="F8" s="2">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H8">
@@ -1958,7 +1958,7 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="6" t="s">
         <v>63</v>
       </c>
       <c r="H9">
